--- a/packages/search-pages/content/downloads/files/customer-list-template/customer-list.xlsx
+++ b/packages/search-pages/content/downloads/files/customer-list-template/customer-list.xlsx
@@ -85,25 +85,25 @@
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
